--- a/docs/FastMark-API-Danh-Sach.xlsx
+++ b/docs/FastMark-API-Danh-Sach.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F202"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1856,16 +1856,16 @@
         <v>POST</v>
       </c>
       <c r="C73" t="str">
-        <v>/api/auth/forgot-password/reset</v>
+        <v>/api/auth/forgot-password/request-me</v>
       </c>
       <c r="D73" t="str">
-        <v>Đặt lại mật khẩu</v>
+        <v>Request Password Reset For Me</v>
       </c>
       <c r="E73" t="str">
-        <v>Body: { resetToken, newPassword }</v>
+        <v>Header: Bearer token (User); Body: JSON theo controller</v>
       </c>
       <c r="F73" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "message": "Success", "data": {...} }</v>
       </c>
     </row>
     <row r="74">
@@ -1876,16 +1876,16 @@
         <v>POST</v>
       </c>
       <c r="C74" t="str">
-        <v>/api/auth/forgot-password/verify</v>
+        <v>/api/auth/forgot-password/reset</v>
       </c>
       <c r="D74" t="str">
-        <v>Xác minh OTP quên mật khẩu</v>
+        <v>Đặt lại mật khẩu</v>
       </c>
       <c r="E74" t="str">
-        <v>Body: { email, otp }</v>
+        <v>Body: { resetToken, newPassword }</v>
       </c>
       <c r="F74" t="str">
-        <v>{ "success": true, "data": { "resetToken" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="75">
@@ -1896,16 +1896,16 @@
         <v>POST</v>
       </c>
       <c r="C75" t="str">
-        <v>/api/auth/google</v>
+        <v>/api/auth/forgot-password/verify</v>
       </c>
       <c r="D75" t="str">
-        <v>Đăng ký/đăng nhập Google</v>
+        <v>Xác minh OTP quên mật khẩu</v>
       </c>
       <c r="E75" t="str">
-        <v>Body: { idToken, userName?, fullName? }</v>
+        <v>Body: { email, otp }</v>
       </c>
       <c r="F75" t="str">
-        <v>{ "success": true, "data": { "customToken", "user" } }</v>
+        <v>{ "success": true, "data": { "resetToken" } }</v>
       </c>
     </row>
     <row r="76">
@@ -1913,19 +1913,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C76" t="str">
-        <v>/api/auth/lock-appeal</v>
+        <v>/api/auth/google</v>
       </c>
       <c r="D76" t="str">
-        <v>Trạng thái khiếu nại khóa tài khoản</v>
+        <v>Đăng ký/đăng nhập Google</v>
       </c>
       <c r="E76" t="str">
-        <v>Header: Bearer token (User bị khóa)</v>
+        <v>Body: { idToken, userName?, fullName? }</v>
       </c>
       <c r="F76" t="str">
-        <v>{ "success": true, "data": { "appeal" } }</v>
+        <v>{ "success": true, "data": { "customToken", "user" } }</v>
       </c>
     </row>
     <row r="77">
@@ -1933,19 +1933,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C77" t="str">
         <v>/api/auth/lock-appeal</v>
       </c>
       <c r="D77" t="str">
-        <v>Gửi khiếu nại khóa tài khoản</v>
+        <v>Trạng thái khiếu nại khóa tài khoản</v>
       </c>
       <c r="E77" t="str">
-        <v>Header: Bearer token; Body: { content, images? }</v>
+        <v>Header: Bearer token (User bị khóa)</v>
       </c>
       <c r="F77" t="str">
-        <v>{ "success": true, "data": { "report" } }</v>
+        <v>{ "success": true, "data": { "appeal" } }</v>
       </c>
     </row>
     <row r="78">
@@ -1956,16 +1956,16 @@
         <v>POST</v>
       </c>
       <c r="C78" t="str">
-        <v>/api/auth/login/email</v>
+        <v>/api/auth/lock-appeal</v>
       </c>
       <c r="D78" t="str">
-        <v>Đăng nhập email</v>
+        <v>Gửi khiếu nại khóa tài khoản</v>
       </c>
       <c r="E78" t="str">
-        <v>Body: { email|userName, password }</v>
+        <v>Header: Bearer token; Body: { content, images? }</v>
       </c>
       <c r="F78" t="str">
-        <v>{ "success": true, "message": "Đăng nhập email thành công.", "data": { "customToken", "user" } }</v>
+        <v>{ "success": true, "data": { "report" } }</v>
       </c>
     </row>
     <row r="79">
@@ -1973,19 +1973,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C79" t="str">
-        <v>/api/auth/me</v>
+        <v>/api/auth/login/email</v>
       </c>
       <c r="D79" t="str">
-        <v>Lấy thông tin tài khoản hiện tại</v>
+        <v>Đăng nhập email</v>
       </c>
       <c r="E79" t="str">
-        <v>Header: Bearer token (User, cho phép bị khóa)</v>
+        <v>Body: { email|userName, password }</v>
       </c>
       <c r="F79" t="str">
-        <v>{ "success": true, "data": { "user", "shop?", "wallet?" } }</v>
+        <v>{ "success": true, "message": "Đăng nhập email thành công.", "data": { "customToken", "user" } }</v>
       </c>
     </row>
     <row r="80">
@@ -1993,19 +1993,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>PUT</v>
+        <v>GET</v>
       </c>
       <c r="C80" t="str">
         <v>/api/auth/me</v>
       </c>
       <c r="D80" t="str">
-        <v>Cập nhật hồ sơ cá nhân</v>
+        <v>Lấy thông tin tài khoản hiện tại</v>
       </c>
       <c r="E80" t="str">
-        <v>Header: Bearer token (User); Body: { fullName?, phone?, ... }</v>
+        <v>Header: Bearer token (User, cho phép bị khóa)</v>
       </c>
       <c r="F80" t="str">
-        <v>{ "success": true, "data": { "user" } }</v>
+        <v>{ "success": true, "data": { "user", "shop?", "wallet?" } }</v>
       </c>
     </row>
     <row r="81">
@@ -2013,19 +2013,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>POST</v>
+        <v>PUT</v>
       </c>
       <c r="C81" t="str">
-        <v>/api/auth/presence/offline</v>
+        <v>/api/auth/me</v>
       </c>
       <c r="D81" t="str">
-        <v>Tắt trạng thái online user</v>
+        <v>Cập nhật hồ sơ cá nhân</v>
       </c>
       <c r="E81" t="str">
-        <v>Header: Bearer token (User)</v>
+        <v>Header: Bearer token (User); Body: { fullName?, phone?, ... }</v>
       </c>
       <c r="F81" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "user" } }</v>
       </c>
     </row>
     <row r="82">
@@ -2036,10 +2036,10 @@
         <v>POST</v>
       </c>
       <c r="C82" t="str">
-        <v>/api/auth/presence/online</v>
+        <v>/api/auth/presence/offline</v>
       </c>
       <c r="D82" t="str">
-        <v>Bật trạng thái online user</v>
+        <v>Tắt trạng thái online user</v>
       </c>
       <c r="E82" t="str">
         <v>Header: Bearer token (User)</v>
@@ -2056,13 +2056,13 @@
         <v>POST</v>
       </c>
       <c r="C83" t="str">
-        <v>/api/auth/presence/shop/offline</v>
+        <v>/api/auth/presence/online</v>
       </c>
       <c r="D83" t="str">
-        <v>Tắt trạng thái online shop</v>
+        <v>Bật trạng thái online user</v>
       </c>
       <c r="E83" t="str">
-        <v>Header: Bearer token (Seller)</v>
+        <v>Header: Bearer token (User)</v>
       </c>
       <c r="F83" t="str">
         <v>{ "success": true }</v>
@@ -2076,10 +2076,10 @@
         <v>POST</v>
       </c>
       <c r="C84" t="str">
-        <v>/api/auth/presence/shop/online</v>
+        <v>/api/auth/presence/shop/offline</v>
       </c>
       <c r="D84" t="str">
-        <v>Bật trạng thái online shop</v>
+        <v>Tắt trạng thái online shop</v>
       </c>
       <c r="E84" t="str">
         <v>Header: Bearer token (Seller)</v>
@@ -2096,16 +2096,16 @@
         <v>POST</v>
       </c>
       <c r="C85" t="str">
-        <v>/api/auth/register/availability</v>
+        <v>/api/auth/presence/shop/online</v>
       </c>
       <c r="D85" t="str">
-        <v>Kiểm tra email/username còn trống</v>
+        <v>Bật trạng thái online shop</v>
       </c>
       <c r="E85" t="str">
-        <v>Body: { email?, userName? }</v>
+        <v>Header: Bearer token (Seller)</v>
       </c>
       <c r="F85" t="str">
-        <v>{ "success": true, "data": { "emailTaken", "userNameTaken" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="86">
@@ -2116,16 +2116,16 @@
         <v>POST</v>
       </c>
       <c r="C86" t="str">
-        <v>/api/auth/register/email</v>
+        <v>/api/auth/register/availability</v>
       </c>
       <c r="D86" t="str">
-        <v>Đăng ký tài khoản email</v>
+        <v>Kiểm tra email/username còn trống</v>
       </c>
       <c r="E86" t="str">
-        <v>Body: { email, password, fullName, userName }</v>
+        <v>Body: { email?, userName? }</v>
       </c>
       <c r="F86" t="str">
-        <v>{ "success": true, "message": "Đăng ký email thành công.", "data": { "customToken", "user" } }</v>
+        <v>{ "success": true, "data": { "emailTaken", "userNameTaken" } }</v>
       </c>
     </row>
     <row r="87">
@@ -2133,19 +2133,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C87" t="str">
-        <v>/api/auth/shop-lock-appeal</v>
+        <v>/api/auth/register/email</v>
       </c>
       <c r="D87" t="str">
-        <v>Trạng thái khiếu nại khóa shop</v>
+        <v>Đăng ký tài khoản email</v>
       </c>
       <c r="E87" t="str">
-        <v>Header: Bearer token (User)</v>
+        <v>Body: { email, password, fullName, userName }</v>
       </c>
       <c r="F87" t="str">
-        <v>{ "success": true, "data": { "appeal" } }</v>
+        <v>{ "success": true, "message": "Đăng ký email thành công.", "data": { "customToken", "user" } }</v>
       </c>
     </row>
     <row r="88">
@@ -2153,19 +2153,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C88" t="str">
         <v>/api/auth/shop-lock-appeal</v>
       </c>
       <c r="D88" t="str">
-        <v>Gửi khiếu nại khóa shop</v>
+        <v>Trạng thái khiếu nại khóa shop</v>
       </c>
       <c r="E88" t="str">
-        <v>Header: Bearer token; Body: { content, images? }</v>
+        <v>Header: Bearer token (User)</v>
       </c>
       <c r="F88" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "appeal" } }</v>
       </c>
     </row>
     <row r="89">
@@ -2176,13 +2176,13 @@
         <v>POST</v>
       </c>
       <c r="C89" t="str">
-        <v>/api/auth/verify-email/confirm</v>
+        <v>/api/auth/shop-lock-appeal</v>
       </c>
       <c r="D89" t="str">
-        <v>Xác nhận OTP email</v>
+        <v>Gửi khiếu nại khóa shop</v>
       </c>
       <c r="E89" t="str">
-        <v>Header: Bearer token (User); Body: { otp }</v>
+        <v>Header: Bearer token; Body: { content, images? }</v>
       </c>
       <c r="F89" t="str">
         <v>{ "success": true }</v>
@@ -2196,13 +2196,13 @@
         <v>POST</v>
       </c>
       <c r="C90" t="str">
-        <v>/api/auth/verify-email/request</v>
+        <v>/api/auth/verify-email/confirm</v>
       </c>
       <c r="D90" t="str">
-        <v>Gửi OTP xác minh email</v>
+        <v>Xác nhận OTP email</v>
       </c>
       <c r="E90" t="str">
-        <v>Header: Bearer token (User)</v>
+        <v>Header: Bearer token (User); Body: { otp }</v>
       </c>
       <c r="F90" t="str">
         <v>{ "success": true }</v>
@@ -2216,13 +2216,13 @@
         <v>POST</v>
       </c>
       <c r="C91" t="str">
-        <v>/api/banners/:id/click</v>
+        <v>/api/auth/verify-email/request</v>
       </c>
       <c r="D91" t="str">
-        <v>Ghi nhận click banner</v>
+        <v>Gửi OTP xác minh email</v>
       </c>
       <c r="E91" t="str">
-        <v>Path: :id</v>
+        <v>Header: Bearer token (User)</v>
       </c>
       <c r="F91" t="str">
         <v>{ "success": true }</v>
@@ -2233,19 +2233,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C92" t="str">
-        <v>/api/banners/active</v>
+        <v>/api/banners/:id/click</v>
       </c>
       <c r="D92" t="str">
-        <v>Banner đang hiển thị</v>
+        <v>Ghi nhận click banner</v>
       </c>
       <c r="E92" t="str">
-        <v>—</v>
+        <v>Path: :id</v>
       </c>
       <c r="F92" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="93">
@@ -2256,16 +2256,16 @@
         <v>GET</v>
       </c>
       <c r="C93" t="str">
-        <v>/api/buyer/favorites</v>
+        <v>/api/banners/active</v>
       </c>
       <c r="D93" t="str">
-        <v>Sản phẩm yêu thích</v>
+        <v>Banner đang hiển thị</v>
       </c>
       <c r="E93" t="str">
-        <v>Header: Bearer token; Query: page?</v>
+        <v>—</v>
       </c>
       <c r="F93" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="94">
@@ -2273,19 +2273,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C94" t="str">
         <v>/api/buyer/favorites</v>
       </c>
       <c r="D94" t="str">
-        <v>Thêm yêu thích</v>
+        <v>Sản phẩm yêu thích</v>
       </c>
       <c r="E94" t="str">
-        <v>Header: Bearer token; Body: { productId }</v>
+        <v>Header: Bearer token; Query: page?</v>
       </c>
       <c r="F94" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="95">
@@ -2293,16 +2293,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C95" t="str">
-        <v>/api/buyer/favorites/:productId</v>
+        <v>/api/buyer/favorites</v>
       </c>
       <c r="D95" t="str">
-        <v>Bỏ yêu thích</v>
+        <v>Thêm yêu thích</v>
       </c>
       <c r="E95" t="str">
-        <v>Header: Bearer token; Path: :productId</v>
+        <v>Header: Bearer token; Body: { productId }</v>
       </c>
       <c r="F95" t="str">
         <v>{ "success": true }</v>
@@ -2313,19 +2313,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>GET</v>
+        <v>DELETE</v>
       </c>
       <c r="C96" t="str">
-        <v>/api/buyer/favorites/ids</v>
+        <v>/api/buyer/favorites/:productId</v>
       </c>
       <c r="D96" t="str">
-        <v>ID sản phẩm yêu thích</v>
+        <v>Bỏ yêu thích</v>
       </c>
       <c r="E96" t="str">
-        <v>Header: Bearer token</v>
+        <v>Header: Bearer token; Path: :productId</v>
       </c>
       <c r="F96" t="str">
-        <v>{ "success": true, "data": { "ids" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="97">
@@ -2333,19 +2333,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>DELETE</v>
+        <v>GET</v>
       </c>
       <c r="C97" t="str">
-        <v>/api/buyer/follows</v>
+        <v>/api/buyer/favorites/ids</v>
       </c>
       <c r="D97" t="str">
-        <v>Bỏ theo dõi shop</v>
+        <v>ID sản phẩm yêu thích</v>
       </c>
       <c r="E97" t="str">
-        <v>Header: Bearer token; Path: :targetId hoặc Body: { shopId }</v>
+        <v>Header: Bearer token</v>
       </c>
       <c r="F97" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "ids" } }</v>
       </c>
     </row>
     <row r="98">
@@ -2353,16 +2353,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>POST</v>
+        <v>DELETE</v>
       </c>
       <c r="C98" t="str">
         <v>/api/buyer/follows</v>
       </c>
       <c r="D98" t="str">
-        <v>Theo dõi shop</v>
+        <v>Bỏ theo dõi shop</v>
       </c>
       <c r="E98" t="str">
-        <v>Header: Bearer token; Body: { shopId }</v>
+        <v>Header: Bearer token; Path: :targetId hoặc Body: { shopId }</v>
       </c>
       <c r="F98" t="str">
         <v>{ "success": true }</v>
@@ -2373,16 +2373,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C99" t="str">
-        <v>/api/buyer/follows/:targetId</v>
+        <v>/api/buyer/follows</v>
       </c>
       <c r="D99" t="str">
-        <v>Bỏ theo dõi shop</v>
+        <v>Theo dõi shop</v>
       </c>
       <c r="E99" t="str">
-        <v>Header: Bearer token; Path: :targetId hoặc Body: { shopId }</v>
+        <v>Header: Bearer token; Body: { shopId }</v>
       </c>
       <c r="F99" t="str">
         <v>{ "success": true }</v>
@@ -2393,19 +2393,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>GET</v>
+        <v>DELETE</v>
       </c>
       <c r="C100" t="str">
-        <v>/api/buyer/follows/followers</v>
+        <v>/api/buyer/follows/:targetId</v>
       </c>
       <c r="D100" t="str">
-        <v>Người theo dõi shop/user</v>
+        <v>Bỏ theo dõi shop</v>
       </c>
       <c r="E100" t="str">
-        <v>Header: Bearer token</v>
+        <v>Header: Bearer token; Path: :targetId hoặc Body: { shopId }</v>
       </c>
       <c r="F100" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="101">
@@ -2416,10 +2416,10 @@
         <v>GET</v>
       </c>
       <c r="C101" t="str">
-        <v>/api/buyer/follows/following</v>
+        <v>/api/buyer/follows/followers</v>
       </c>
       <c r="D101" t="str">
-        <v>Shop đang theo dõi</v>
+        <v>Người theo dõi shop/user</v>
       </c>
       <c r="E101" t="str">
         <v>Header: Bearer token</v>
@@ -2436,16 +2436,16 @@
         <v>GET</v>
       </c>
       <c r="C102" t="str">
-        <v>/api/buyer/follows/status</v>
+        <v>/api/buyer/follows/following</v>
       </c>
       <c r="D102" t="str">
-        <v>Trạng thái follow shop</v>
+        <v>Shop đang theo dõi</v>
       </c>
       <c r="E102" t="str">
-        <v>Header: Bearer token; Query: shopId</v>
+        <v>Header: Bearer token</v>
       </c>
       <c r="F102" t="str">
-        <v>{ "success": true, "data": { "following" } }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="103">
@@ -2456,16 +2456,16 @@
         <v>GET</v>
       </c>
       <c r="C103" t="str">
-        <v>/api/buyer/orders</v>
+        <v>/api/buyer/follows/status</v>
       </c>
       <c r="D103" t="str">
-        <v>Danh sách đơn (buyer/seller)</v>
+        <v>Trạng thái follow shop</v>
       </c>
       <c r="E103" t="str">
-        <v>Header: Bearer token; Query: tab?, search?</v>
+        <v>Header: Bearer token; Query: shopId</v>
       </c>
       <c r="F103" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true, "data": { "following" } }</v>
       </c>
     </row>
     <row r="104">
@@ -2473,19 +2473,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C104" t="str">
-        <v>/api/buyer/reports</v>
+        <v>/api/buyer/orders</v>
       </c>
       <c r="D104" t="str">
-        <v>Buyer báo cáo vi phạm</v>
+        <v>Danh sách đơn (buyer/seller)</v>
       </c>
       <c r="E104" t="str">
-        <v>Header: Bearer token; Body: { reportType, content, ... }</v>
+        <v>Header: Bearer token; Query: tab?, search?</v>
       </c>
       <c r="F104" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="105">
@@ -2496,16 +2496,16 @@
         <v>POST</v>
       </c>
       <c r="C105" t="str">
-        <v>/api/buyer/reservations</v>
+        <v>/api/buyer/reports</v>
       </c>
       <c r="D105" t="str">
-        <v>Tạo đơn giữ hàng</v>
+        <v>Buyer báo cáo vi phạm</v>
       </c>
       <c r="E105" t="str">
-        <v>Header: Bearer token; Body: { productId, variantId, quantity, pickupTime, note? }</v>
+        <v>Header: Bearer token; Body: { reportType, content, ... }</v>
       </c>
       <c r="F105" t="str">
-        <v>{ "success": true, "data": { "reservation" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="106">
@@ -2513,16 +2513,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C106" t="str">
-        <v>/api/buyer/reservations/:id</v>
+        <v>/api/buyer/reservations</v>
       </c>
       <c r="D106" t="str">
-        <v>Chi tiết đơn buyer</v>
+        <v>Tạo đơn giữ hàng</v>
       </c>
       <c r="E106" t="str">
-        <v>Header: Bearer token; Path: :id</v>
+        <v>Header: Bearer token; Body: { productId, variantId, quantity, pickupTime, note? }</v>
       </c>
       <c r="F106" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -2533,16 +2533,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C107" t="str">
-        <v>/api/buyer/reservations/:id/cancel</v>
+        <v>/api/buyer/reservations/:id</v>
       </c>
       <c r="D107" t="str">
-        <v>Hủy đơn giữ hàng</v>
+        <v>Chi tiết đơn buyer</v>
       </c>
       <c r="E107" t="str">
-        <v>Header: Bearer token; Path: :id; Body: { reason?, images? }</v>
+        <v>Header: Bearer token; Path: :id</v>
       </c>
       <c r="F107" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -2556,13 +2556,13 @@
         <v>POST</v>
       </c>
       <c r="C108" t="str">
-        <v>/api/buyer/reservations/:id/confirm-received</v>
+        <v>/api/buyer/reservations/:id/cancel</v>
       </c>
       <c r="D108" t="str">
-        <v>Buyer xác nhận đã nhận hàng (QR)</v>
+        <v>Hủy đơn giữ hàng</v>
       </c>
       <c r="E108" t="str">
-        <v>Header: Bearer token; Body: { reservationId, scannedShopId }</v>
+        <v>Header: Bearer token; Path: :id; Body: { reason?, images? }</v>
       </c>
       <c r="F108" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -2576,13 +2576,13 @@
         <v>POST</v>
       </c>
       <c r="C109" t="str">
-        <v>/api/buyer/reservations/:id/forfeit-deposit</v>
+        <v>/api/buyer/reservations/:id/confirm-received</v>
       </c>
       <c r="D109" t="str">
-        <v>Buyer đồng ý mất cọc</v>
+        <v>Buyer xác nhận đã nhận hàng (QR)</v>
       </c>
       <c r="E109" t="str">
-        <v>Header: Bearer token; Body/Path: reservationId</v>
+        <v>Header: Bearer token; Body: { reservationId, scannedShopId }</v>
       </c>
       <c r="F109" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -2596,16 +2596,16 @@
         <v>POST</v>
       </c>
       <c r="C110" t="str">
-        <v>/api/buyer/reservations/:id/report</v>
+        <v>/api/buyer/reservations/:id/forfeit-deposit</v>
       </c>
       <c r="D110" t="str">
-        <v>Buyer báo cáo tranh chấp đơn</v>
+        <v>Buyer đồng ý mất cọc</v>
       </c>
       <c r="E110" t="str">
-        <v>Header: Bearer token; Body: { reason, description, latitude, longitude, images }</v>
+        <v>Header: Bearer token; Body/Path: reservationId</v>
       </c>
       <c r="F110" t="str">
-        <v>{ "success": true, "data": { "report", "reservation" } }</v>
+        <v>{ "success": true, "data": { "reservation" } }</v>
       </c>
     </row>
     <row r="111">
@@ -2616,16 +2616,16 @@
         <v>POST</v>
       </c>
       <c r="C111" t="str">
-        <v>/api/buyer/reservations/confirm-received</v>
+        <v>/api/buyer/reservations/:id/report</v>
       </c>
       <c r="D111" t="str">
-        <v>Buyer xác nhận đã nhận hàng (QR)</v>
+        <v>Buyer báo cáo tranh chấp đơn</v>
       </c>
       <c r="E111" t="str">
-        <v>Header: Bearer token; Body: { reservationId, scannedShopId }</v>
+        <v>Header: Bearer token; Body: { reason, description, latitude, longitude, images }</v>
       </c>
       <c r="F111" t="str">
-        <v>{ "success": true, "data": { "reservation" } }</v>
+        <v>{ "success": true, "data": { "report", "reservation" } }</v>
       </c>
     </row>
     <row r="112">
@@ -2636,13 +2636,13 @@
         <v>POST</v>
       </c>
       <c r="C112" t="str">
-        <v>/api/buyer/reservations/forfeit-deposit</v>
+        <v>/api/buyer/reservations/confirm-received</v>
       </c>
       <c r="D112" t="str">
-        <v>Buyer đồng ý mất cọc</v>
+        <v>Buyer xác nhận đã nhận hàng (QR)</v>
       </c>
       <c r="E112" t="str">
-        <v>Header: Bearer token; Body/Path: reservationId</v>
+        <v>Header: Bearer token; Body: { reservationId, scannedShopId }</v>
       </c>
       <c r="F112" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -2656,16 +2656,16 @@
         <v>POST</v>
       </c>
       <c r="C113" t="str">
-        <v>/api/buyer/reservations/report</v>
+        <v>/api/buyer/reservations/forfeit-deposit</v>
       </c>
       <c r="D113" t="str">
-        <v>Buyer báo cáo tranh chấp đơn</v>
+        <v>Buyer đồng ý mất cọc</v>
       </c>
       <c r="E113" t="str">
-        <v>Header: Bearer token; Body: { reason, description, latitude, longitude, images }</v>
+        <v>Header: Bearer token; Body/Path: reservationId</v>
       </c>
       <c r="F113" t="str">
-        <v>{ "success": true, "data": { "report", "reservation" } }</v>
+        <v>{ "success": true, "data": { "reservation" } }</v>
       </c>
     </row>
     <row r="114">
@@ -2676,16 +2676,16 @@
         <v>POST</v>
       </c>
       <c r="C114" t="str">
-        <v>/api/buyer/reservations/validate-shop-qr</v>
+        <v>/api/buyer/reservations/report</v>
       </c>
       <c r="D114" t="str">
-        <v>Kiểm tra QR shop hợp lệ</v>
+        <v>Buyer báo cáo tranh chấp đơn</v>
       </c>
       <c r="E114" t="str">
-        <v>Header: Bearer token; Body: { reservationId, scannedShopId }</v>
+        <v>Header: Bearer token; Body: { reason, description, latitude, longitude, images }</v>
       </c>
       <c r="F114" t="str">
-        <v>{ "success": true, "data": { "ok": true } }</v>
+        <v>{ "success": true, "data": { "report", "reservation" } }</v>
       </c>
     </row>
     <row r="115">
@@ -2693,19 +2693,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C115" t="str">
-        <v>/api/buyer/reviews</v>
+        <v>/api/buyer/reservations/validate-shop-qr</v>
       </c>
       <c r="D115" t="str">
-        <v>Danh sách đánh giá</v>
+        <v>Kiểm tra QR shop hợp lệ</v>
       </c>
       <c r="E115" t="str">
-        <v>Header: Bearer token; Query: page?</v>
+        <v>Header: Bearer token; Body: { reservationId, scannedShopId }</v>
       </c>
       <c r="F115" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true, "data": { "ok": true } }</v>
       </c>
     </row>
     <row r="116">
@@ -2713,19 +2713,19 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C116" t="str">
         <v>/api/buyer/reviews</v>
       </c>
       <c r="D116" t="str">
-        <v>Tạo đánh giá</v>
+        <v>Danh sách đánh giá</v>
       </c>
       <c r="E116" t="str">
-        <v>Header: Bearer token; Body: { reservationId, rating, content }</v>
+        <v>Header: Bearer token; Query: page?</v>
       </c>
       <c r="F116" t="str">
-        <v>{ "success": true, "data": { "review" } }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="117">
@@ -2733,19 +2733,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C117" t="str">
-        <v>/api/buyer/reviews/:id</v>
+        <v>/api/buyer/reviews</v>
       </c>
       <c r="D117" t="str">
-        <v>Xóa đánh giá</v>
+        <v>Tạo đánh giá</v>
       </c>
       <c r="E117" t="str">
-        <v>Header: Bearer token; Path: :id</v>
+        <v>Header: Bearer token; Body: { reservationId, rating, content }</v>
       </c>
       <c r="F117" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "review" } }</v>
       </c>
     </row>
     <row r="118">
@@ -2753,16 +2753,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>PUT</v>
+        <v>DELETE</v>
       </c>
       <c r="C118" t="str">
         <v>/api/buyer/reviews/:id</v>
       </c>
       <c r="D118" t="str">
-        <v>Sửa đánh giá</v>
+        <v>Xóa đánh giá</v>
       </c>
       <c r="E118" t="str">
-        <v>Header: Bearer token; Path: :id; Body: fields</v>
+        <v>Header: Bearer token; Path: :id</v>
       </c>
       <c r="F118" t="str">
         <v>{ "success": true }</v>
@@ -2773,19 +2773,19 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>GET</v>
+        <v>PUT</v>
       </c>
       <c r="C119" t="str">
-        <v>/api/buyer/users/:userId</v>
+        <v>/api/buyer/reviews/:id</v>
       </c>
       <c r="D119" t="str">
-        <v>Hồ sơ user public</v>
+        <v>Sửa đánh giá</v>
       </c>
       <c r="E119" t="str">
-        <v>Header: Bearer token; Path: :userId</v>
+        <v>Header: Bearer token; Path: :id; Body: fields</v>
       </c>
       <c r="F119" t="str">
-        <v>{ "success": true, "data": { "user" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="120">
@@ -2796,16 +2796,16 @@
         <v>GET</v>
       </c>
       <c r="C120" t="str">
-        <v>/api/buyer/users/:userId/following</v>
+        <v>/api/buyer/users/:userId</v>
       </c>
       <c r="D120" t="str">
-        <v>Shop user đang theo dõi</v>
+        <v>Hồ sơ user public</v>
       </c>
       <c r="E120" t="str">
         <v>Header: Bearer token; Path: :userId</v>
       </c>
       <c r="F120" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true, "data": { "user" } }</v>
       </c>
     </row>
     <row r="121">
@@ -2816,13 +2816,13 @@
         <v>GET</v>
       </c>
       <c r="C121" t="str">
-        <v>/api/buyer/users/search</v>
+        <v>/api/buyer/users/:userId/following</v>
       </c>
       <c r="D121" t="str">
-        <v>Tìm user</v>
+        <v>Shop user đang theo dõi</v>
       </c>
       <c r="E121" t="str">
-        <v>Header: Bearer token; Query: q</v>
+        <v>Header: Bearer token; Path: :userId</v>
       </c>
       <c r="F121" t="str">
         <v>{ "success": true, "data": { "items" } }</v>
@@ -2836,16 +2836,16 @@
         <v>GET</v>
       </c>
       <c r="C122" t="str">
-        <v>/api/categories/</v>
+        <v>/api/buyer/users/search</v>
       </c>
       <c r="D122" t="str">
-        <v>Danh mục sản phẩm public</v>
+        <v>Tìm user</v>
       </c>
       <c r="E122" t="str">
-        <v>—</v>
+        <v>Header: Bearer token; Query: q</v>
       </c>
       <c r="F122" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="123">
@@ -2853,19 +2853,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C123" t="str">
         <v>/api/categories/</v>
       </c>
       <c r="D123" t="str">
-        <v>Tạo DM (legacy)</v>
+        <v>Danh mục sản phẩm public</v>
       </c>
       <c r="E123" t="str">
-        <v>Header: Bearer token (Admin)</v>
+        <v>—</v>
       </c>
       <c r="F123" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="124">
@@ -2873,16 +2873,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C124" t="str">
-        <v>/api/categories/:id</v>
+        <v>/api/categories/</v>
       </c>
       <c r="D124" t="str">
-        <v>Xóa DM (legacy)</v>
+        <v>Tạo DM (legacy)</v>
       </c>
       <c r="E124" t="str">
-        <v>Header: Bearer token (Admin); Path: :id</v>
+        <v>Header: Bearer token (Admin)</v>
       </c>
       <c r="F124" t="str">
         <v>{ "success": true }</v>
@@ -2893,13 +2893,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>PUT</v>
+        <v>DELETE</v>
       </c>
       <c r="C125" t="str">
         <v>/api/categories/:id</v>
       </c>
       <c r="D125" t="str">
-        <v>Sửa DM (legacy)</v>
+        <v>Xóa DM (legacy)</v>
       </c>
       <c r="E125" t="str">
         <v>Header: Bearer token (Admin); Path: :id</v>
@@ -2913,19 +2913,19 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>GET</v>
+        <v>PUT</v>
       </c>
       <c r="C126" t="str">
-        <v>/api/categories/products</v>
+        <v>/api/categories/:id</v>
       </c>
       <c r="D126" t="str">
-        <v>DM SP admin</v>
+        <v>Sửa DM (legacy)</v>
       </c>
       <c r="E126" t="str">
-        <v>Header: Bearer token (Admin)</v>
+        <v>Header: Bearer token (Admin); Path: :id</v>
       </c>
       <c r="F126" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="127">
@@ -2933,19 +2933,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C127" t="str">
         <v>/api/categories/products</v>
       </c>
       <c r="D127" t="str">
-        <v>Tạo DM SP</v>
+        <v>DM SP admin</v>
       </c>
       <c r="E127" t="str">
-        <v>Header: Bearer token (Admin); Body: { name }</v>
+        <v>Header: Bearer token (Admin)</v>
       </c>
       <c r="F127" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="128">
@@ -2953,16 +2953,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C128" t="str">
-        <v>/api/categories/products/:id</v>
+        <v>/api/categories/products</v>
       </c>
       <c r="D128" t="str">
-        <v>Xóa DM SP</v>
+        <v>Tạo DM SP</v>
       </c>
       <c r="E128" t="str">
-        <v>Header: Bearer token (Admin); Path: :id</v>
+        <v>Header: Bearer token (Admin); Body: { name }</v>
       </c>
       <c r="F128" t="str">
         <v>{ "success": true }</v>
@@ -2973,13 +2973,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>PUT</v>
+        <v>DELETE</v>
       </c>
       <c r="C129" t="str">
         <v>/api/categories/products/:id</v>
       </c>
       <c r="D129" t="str">
-        <v>Sửa DM SP</v>
+        <v>Xóa DM SP</v>
       </c>
       <c r="E129" t="str">
         <v>Header: Bearer token (Admin); Path: :id</v>
@@ -2993,16 +2993,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>POST</v>
+        <v>PUT</v>
       </c>
       <c r="C130" t="str">
-        <v>/api/categories/products/:id/icon</v>
+        <v>/api/categories/products/:id</v>
       </c>
       <c r="D130" t="str">
-        <v>Upload icon DM SP</v>
+        <v>Sửa DM SP</v>
       </c>
       <c r="E130" t="str">
-        <v>Header: Bearer token (Admin); multipart icon</v>
+        <v>Header: Bearer token (Admin); Path: :id</v>
       </c>
       <c r="F130" t="str">
         <v>{ "success": true }</v>
@@ -3013,19 +3013,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C131" t="str">
-        <v>/api/categories/shops</v>
+        <v>/api/categories/products/:id/icon</v>
       </c>
       <c r="D131" t="str">
-        <v>DM shop admin</v>
+        <v>Upload icon DM SP</v>
       </c>
       <c r="E131" t="str">
-        <v>Header: Bearer token (Admin)</v>
+        <v>Header: Bearer token (Admin); multipart icon</v>
       </c>
       <c r="F131" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="132">
@@ -3033,19 +3033,19 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C132" t="str">
         <v>/api/categories/shops</v>
       </c>
       <c r="D132" t="str">
-        <v>Tạo DM shop</v>
+        <v>DM shop admin</v>
       </c>
       <c r="E132" t="str">
         <v>Header: Bearer token (Admin)</v>
       </c>
       <c r="F132" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="133">
@@ -3053,16 +3053,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C133" t="str">
-        <v>/api/categories/shops/:id</v>
+        <v>/api/categories/shops</v>
       </c>
       <c r="D133" t="str">
-        <v>Xóa DM shop</v>
+        <v>Tạo DM shop</v>
       </c>
       <c r="E133" t="str">
-        <v>Header: Bearer token (Admin); Path: :id</v>
+        <v>Header: Bearer token (Admin)</v>
       </c>
       <c r="F133" t="str">
         <v>{ "success": true }</v>
@@ -3073,13 +3073,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>PUT</v>
+        <v>DELETE</v>
       </c>
       <c r="C134" t="str">
         <v>/api/categories/shops/:id</v>
       </c>
       <c r="D134" t="str">
-        <v>Sửa DM shop</v>
+        <v>Xóa DM shop</v>
       </c>
       <c r="E134" t="str">
         <v>Header: Bearer token (Admin); Path: :id</v>
@@ -3093,19 +3093,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>GET</v>
+        <v>PUT</v>
       </c>
       <c r="C135" t="str">
-        <v>/api/notifications/</v>
+        <v>/api/categories/shops/:id</v>
       </c>
       <c r="D135" t="str">
-        <v>Danh sách thông báo</v>
+        <v>Sửa DM shop</v>
       </c>
       <c r="E135" t="str">
-        <v>Header: Bearer token (User); Query: page?, limit?</v>
+        <v>Header: Bearer token (Admin); Path: :id</v>
       </c>
       <c r="F135" t="str">
-        <v>{ "success": true, "data": { "items", "unreadCount" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="136">
@@ -3113,19 +3113,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C136" t="str">
-        <v>/api/notifications/:id/read</v>
+        <v>/api/notifications/</v>
       </c>
       <c r="D136" t="str">
-        <v>Đánh dấu đọc 1 thông báo</v>
+        <v>Danh sách thông báo</v>
       </c>
       <c r="E136" t="str">
-        <v>Header: Bearer token; Path: :id</v>
+        <v>Header: Bearer token (User); Query: page?, limit?, audience?=buyer|seller</v>
       </c>
       <c r="F136" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "items", "unreadCount", "pagination" } }</v>
       </c>
     </row>
     <row r="137">
@@ -3133,19 +3133,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>DELETE</v>
+        <v>POST</v>
       </c>
       <c r="C137" t="str">
-        <v>/api/notifications/device-token</v>
+        <v>/api/notifications/:id/read</v>
       </c>
       <c r="D137" t="str">
-        <v>Xóa FCM device token</v>
+        <v>Đánh dấu đọc 1 thông báo</v>
       </c>
       <c r="E137" t="str">
-        <v>Header: Bearer token; Body: { token }</v>
+        <v>Header: Bearer token; Path: :id; Query: audience?</v>
       </c>
       <c r="F137" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "unreadCount?", "unreadCounts?" } }</v>
       </c>
     </row>
     <row r="138">
@@ -3153,16 +3153,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>POST</v>
+        <v>DELETE</v>
       </c>
       <c r="C138" t="str">
         <v>/api/notifications/device-token</v>
       </c>
       <c r="D138" t="str">
-        <v>Đăng ký FCM device token</v>
+        <v>Xóa FCM device token</v>
       </c>
       <c r="E138" t="str">
-        <v>Header: Bearer token; Body: { token, platform? }</v>
+        <v>Header: Bearer token; Body: { token }</v>
       </c>
       <c r="F138" t="str">
         <v>{ "success": true }</v>
@@ -3176,13 +3176,13 @@
         <v>POST</v>
       </c>
       <c r="C139" t="str">
-        <v>/api/notifications/read-all</v>
+        <v>/api/notifications/device-token</v>
       </c>
       <c r="D139" t="str">
-        <v>Đánh dấu đọc tất cả thông báo</v>
+        <v>Đăng ký FCM device token</v>
       </c>
       <c r="E139" t="str">
-        <v>Header: Bearer token (User)</v>
+        <v>Header: Bearer token; Body: { token, platform? }</v>
       </c>
       <c r="F139" t="str">
         <v>{ "success": true }</v>
@@ -3193,19 +3193,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C140" t="str">
-        <v>/api/products/</v>
+        <v>/api/notifications/read-all</v>
       </c>
       <c r="D140" t="str">
-        <v>Sản phẩm của seller</v>
+        <v>Đánh dấu đọc tất cả thông báo</v>
       </c>
       <c r="E140" t="str">
-        <v>Header: Bearer token (Seller); Query: page?</v>
+        <v>Header: Bearer token (User); Query/Body: audience?</v>
       </c>
       <c r="F140" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="141">
@@ -3213,19 +3213,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C141" t="str">
-        <v>/api/products/</v>
+        <v>/api/notifications/unread-count</v>
       </c>
       <c r="D141" t="str">
-        <v>Tạo sản phẩm</v>
+        <v>Số thông báo chưa đọc theo audience</v>
       </c>
       <c r="E141" t="str">
-        <v>Header: Bearer token (Seller); Body: product data</v>
+        <v>Header: Bearer token (User); Query: audience?=buyer|seller</v>
       </c>
       <c r="F141" t="str">
-        <v>{ "success": true, "data": { "product" } }</v>
+        <v>{ "success": true, "data": { "unreadCount", "audience" } }</v>
       </c>
     </row>
     <row r="142">
@@ -3233,19 +3233,19 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>DELETE</v>
+        <v>GET</v>
       </c>
       <c r="C142" t="str">
-        <v>/api/products/:id</v>
+        <v>/api/products/</v>
       </c>
       <c r="D142" t="str">
-        <v>Xóa mềm sản phẩm</v>
+        <v>Sản phẩm của seller</v>
       </c>
       <c r="E142" t="str">
-        <v>Header: Bearer token (Seller); Path: :id</v>
+        <v>Header: Bearer token (Seller); Query: page?</v>
       </c>
       <c r="F142" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="143">
@@ -3253,16 +3253,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C143" t="str">
-        <v>/api/products/:id</v>
+        <v>/api/products/</v>
       </c>
       <c r="D143" t="str">
-        <v>Chi tiết sản phẩm</v>
+        <v>Tạo sản phẩm</v>
       </c>
       <c r="E143" t="str">
-        <v>Path: :id</v>
+        <v>Header: Bearer token (Seller); Body: product data</v>
       </c>
       <c r="F143" t="str">
         <v>{ "success": true, "data": { "product" } }</v>
@@ -3273,13 +3273,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>PUT</v>
+        <v>DELETE</v>
       </c>
       <c r="C144" t="str">
         <v>/api/products/:id</v>
       </c>
       <c r="D144" t="str">
-        <v>Cập nhật sản phẩm</v>
+        <v>Xóa mềm sản phẩm</v>
       </c>
       <c r="E144" t="str">
         <v>Header: Bearer token (Seller); Path: :id</v>
@@ -3293,19 +3293,19 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>PUT</v>
+        <v>GET</v>
       </c>
       <c r="C145" t="str">
-        <v>/api/products/:id/pin</v>
+        <v>/api/products/:id</v>
       </c>
       <c r="D145" t="str">
-        <v>Ghim sản phẩm</v>
+        <v>Chi tiết sản phẩm</v>
       </c>
       <c r="E145" t="str">
-        <v>Header: Bearer token (Seller); Path: :id; Body: { pinned }</v>
+        <v>Path: :id</v>
       </c>
       <c r="F145" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "product" } }</v>
       </c>
     </row>
     <row r="146">
@@ -3313,13 +3313,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="str">
-        <v>DELETE</v>
+        <v>PUT</v>
       </c>
       <c r="C146" t="str">
-        <v>/api/products/:id/promotion</v>
+        <v>/api/products/:id</v>
       </c>
       <c r="D146" t="str">
-        <v>Xóa khuyến mãi SP</v>
+        <v>Cập nhật sản phẩm</v>
       </c>
       <c r="E146" t="str">
         <v>Header: Bearer token (Seller); Path: :id</v>
@@ -3333,16 +3333,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="str">
-        <v>POST</v>
+        <v>PUT</v>
       </c>
       <c r="C147" t="str">
-        <v>/api/products/:id/promotion</v>
+        <v>/api/products/:id/pin</v>
       </c>
       <c r="D147" t="str">
-        <v>Đặt khuyến mãi SP</v>
+        <v>Ghim sản phẩm</v>
       </c>
       <c r="E147" t="str">
-        <v>Header: Bearer token (Seller); Path: :id; Body: { discountPercent, ... }</v>
+        <v>Header: Bearer token (Seller); Path: :id; Body: { pinned }</v>
       </c>
       <c r="F147" t="str">
         <v>{ "success": true }</v>
@@ -3353,16 +3353,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="str">
-        <v>PUT</v>
+        <v>DELETE</v>
       </c>
       <c r="C148" t="str">
         <v>/api/products/:id/promotion</v>
       </c>
       <c r="D148" t="str">
-        <v>Đặt khuyến mãi SP</v>
+        <v>Xóa khuyến mãi SP</v>
       </c>
       <c r="E148" t="str">
-        <v>Header: Bearer token (Seller); Path: :id; Body: { discountPercent, ... }</v>
+        <v>Header: Bearer token (Seller); Path: :id</v>
       </c>
       <c r="F148" t="str">
         <v>{ "success": true }</v>
@@ -3373,19 +3373,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C149" t="str">
-        <v>/api/products/categories</v>
+        <v>/api/products/:id/promotion</v>
       </c>
       <c r="D149" t="str">
-        <v>Danh mục sản phẩm public</v>
+        <v>Đặt khuyến mãi SP</v>
       </c>
       <c r="E149" t="str">
-        <v>—</v>
+        <v>Header: Bearer token (Seller); Path: :id; Body: { discountPercent, ... }</v>
       </c>
       <c r="F149" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="150">
@@ -3393,19 +3393,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>GET</v>
+        <v>PUT</v>
       </c>
       <c r="C150" t="str">
-        <v>/api/products/discover</v>
+        <v>/api/products/:id/promotion</v>
       </c>
       <c r="D150" t="str">
-        <v>Khám phá sản phẩm</v>
+        <v>Đặt khuyến mãi SP</v>
       </c>
       <c r="E150" t="str">
-        <v>Query: q?, categoryId?, lat?, lng?</v>
+        <v>Header: Bearer token (Seller); Path: :id; Body: { discountPercent, ... }</v>
       </c>
       <c r="F150" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="151">
@@ -3416,16 +3416,16 @@
         <v>GET</v>
       </c>
       <c r="C151" t="str">
-        <v>/api/products/mine/:id</v>
+        <v>/api/products/categories</v>
       </c>
       <c r="D151" t="str">
-        <v>Chi tiết SP seller</v>
+        <v>Danh mục sản phẩm public</v>
       </c>
       <c r="E151" t="str">
-        <v>Header: Bearer token (Seller); Path: :id</v>
+        <v>—</v>
       </c>
       <c r="F151" t="str">
-        <v>{ "success": true, "data": { "product" } }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="152">
@@ -3436,13 +3436,13 @@
         <v>GET</v>
       </c>
       <c r="C152" t="str">
-        <v>/api/products/promotions</v>
+        <v>/api/products/discover</v>
       </c>
       <c r="D152" t="str">
-        <v>Sản phẩm khuyến mãi</v>
+        <v>Khám phá sản phẩm</v>
       </c>
       <c r="E152" t="str">
-        <v>Query: page?, limit?</v>
+        <v>Query: q?, categoryId?, lat?, lng?</v>
       </c>
       <c r="F152" t="str">
         <v>{ "success": true, "data": { "items" } }</v>
@@ -3453,19 +3453,19 @@
         <v>152</v>
       </c>
       <c r="B153" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C153" t="str">
-        <v>/api/products/promotions/bulk</v>
+        <v>/api/products/mine/:id</v>
       </c>
       <c r="D153" t="str">
-        <v>Khuyến mãi hàng loạt</v>
+        <v>Chi tiết SP seller</v>
       </c>
       <c r="E153" t="str">
-        <v>Header: Bearer token (Seller); Body: { items }</v>
+        <v>Header: Bearer token (Seller); Path: :id</v>
       </c>
       <c r="F153" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "product" } }</v>
       </c>
     </row>
     <row r="154">
@@ -3476,16 +3476,16 @@
         <v>GET</v>
       </c>
       <c r="C154" t="str">
-        <v>/api/products/promotions/mine</v>
+        <v>/api/products/promotions</v>
       </c>
       <c r="D154" t="str">
-        <v>KM của seller</v>
+        <v>Sản phẩm khuyến mãi</v>
       </c>
       <c r="E154" t="str">
-        <v>Header: Bearer token (Seller)</v>
+        <v>Query: page?, limit?</v>
       </c>
       <c r="F154" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="155">
@@ -3496,16 +3496,16 @@
         <v>POST</v>
       </c>
       <c r="C155" t="str">
-        <v>/api/reports/buyer-report-seller</v>
+        <v>/api/products/promotions/bulk</v>
       </c>
       <c r="D155" t="str">
-        <v>Buyer báo seller không có mặt</v>
+        <v>Khuyến mãi hàng loạt</v>
       </c>
       <c r="E155" t="str">
-        <v>Header: Bearer token; Body: { reservationId, reason, description, lat, lng, images }</v>
+        <v>Header: Bearer token (Seller); Body: { items }</v>
       </c>
       <c r="F155" t="str">
-        <v>{ "success": true, "data": { "report" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="156">
@@ -3516,16 +3516,16 @@
         <v>GET</v>
       </c>
       <c r="C156" t="str">
-        <v>/api/reports/reservation/:reservationId</v>
+        <v>/api/products/promotions/mine</v>
       </c>
       <c r="D156" t="str">
-        <v>Báo cáo tranh chấp của đơn</v>
+        <v>KM của seller</v>
       </c>
       <c r="E156" t="str">
-        <v>Header: Bearer token; Path: reservationId</v>
+        <v>Header: Bearer token (Seller)</v>
       </c>
       <c r="F156" t="str">
-        <v>{ "success": true, "data": { "reports" } }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="157">
@@ -3536,13 +3536,13 @@
         <v>POST</v>
       </c>
       <c r="C157" t="str">
-        <v>/api/reports/seller-report-buyer</v>
+        <v>/api/reports/buyer-report-seller</v>
       </c>
       <c r="D157" t="str">
-        <v>Seller báo buyer không đến</v>
+        <v>Buyer báo seller không có mặt</v>
       </c>
       <c r="E157" t="str">
-        <v>Header: Bearer token (Seller); Body: { reservationId, description, lat, lng, images }</v>
+        <v>Header: Bearer token; Body: { reservationId, reason, description, lat, lng, images }</v>
       </c>
       <c r="F157" t="str">
         <v>{ "success": true, "data": { "report" } }</v>
@@ -3556,16 +3556,16 @@
         <v>GET</v>
       </c>
       <c r="C158" t="str">
-        <v>/api/seller/banner</v>
+        <v>/api/reports/reservation/:reservationId</v>
       </c>
       <c r="D158" t="str">
-        <v>Banner quảng cáo của seller</v>
+        <v>Báo cáo tranh chấp của đơn</v>
       </c>
       <c r="E158" t="str">
-        <v>Header: Bearer token (Seller)</v>
+        <v>Header: Bearer token; Path: reservationId</v>
       </c>
       <c r="F158" t="str">
-        <v>{ "success": true, "data": { "banner" } }</v>
+        <v>{ "success": true, "data": { "reports" } }</v>
       </c>
     </row>
     <row r="159">
@@ -3573,19 +3573,19 @@
         <v>158</v>
       </c>
       <c r="B159" t="str">
-        <v>PUT</v>
+        <v>POST</v>
       </c>
       <c r="C159" t="str">
-        <v>/api/seller/banner/creative</v>
+        <v>/api/reports/seller-report-buyer</v>
       </c>
       <c r="D159" t="str">
-        <v>Cập nhật nội dung banner</v>
+        <v>Seller báo buyer không đến</v>
       </c>
       <c r="E159" t="str">
-        <v>Header: Bearer token (Seller); Body: { imageUrl, link? }</v>
+        <v>Header: Bearer token (Seller); Body: { reservationId, description, lat, lng, images }</v>
       </c>
       <c r="F159" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "report" } }</v>
       </c>
     </row>
     <row r="160">
@@ -3593,19 +3593,19 @@
         <v>159</v>
       </c>
       <c r="B160" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C160" t="str">
-        <v>/api/seller/banner/purchase</v>
+        <v>/api/seller/banner</v>
       </c>
       <c r="D160" t="str">
-        <v>Mua banner quảng cáo</v>
+        <v>Banner quảng cáo của seller</v>
       </c>
       <c r="E160" t="str">
-        <v>Header: Bearer token (Seller); Body: { planId }</v>
+        <v>Header: Bearer token (Seller)</v>
       </c>
       <c r="F160" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "banner" } }</v>
       </c>
     </row>
     <row r="161">
@@ -3613,19 +3613,19 @@
         <v>160</v>
       </c>
       <c r="B161" t="str">
-        <v>GET</v>
+        <v>PUT</v>
       </c>
       <c r="C161" t="str">
-        <v>/api/seller/orders</v>
+        <v>/api/seller/banner/creative</v>
       </c>
       <c r="D161" t="str">
-        <v>Danh sách đơn (buyer/seller)</v>
+        <v>Cập nhật nội dung banner</v>
       </c>
       <c r="E161" t="str">
-        <v>Header: Bearer token; Query: tab?, search?</v>
+        <v>Header: Bearer token (Seller); Body: { imageUrl, link? }</v>
       </c>
       <c r="F161" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="162">
@@ -3636,13 +3636,13 @@
         <v>POST</v>
       </c>
       <c r="C162" t="str">
-        <v>/api/seller/phone-code/confirm</v>
+        <v>/api/seller/banner/purchase</v>
       </c>
       <c r="D162" t="str">
-        <v>Xác nhận OTP SĐT seller</v>
+        <v>Mua banner quảng cáo</v>
       </c>
       <c r="E162" t="str">
-        <v>Header: Bearer token; Body: { phone, code }</v>
+        <v>Header: Bearer token (Seller); Body: { planId }</v>
       </c>
       <c r="F162" t="str">
         <v>{ "success": true }</v>
@@ -3653,19 +3653,19 @@
         <v>162</v>
       </c>
       <c r="B163" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C163" t="str">
-        <v>/api/seller/phone-code/request</v>
+        <v>/api/seller/orders</v>
       </c>
       <c r="D163" t="str">
-        <v>Gửi OTP xác minh SĐT seller</v>
+        <v>Danh sách đơn (buyer/seller)</v>
       </c>
       <c r="E163" t="str">
-        <v>Header: Bearer token; Body: { phone }</v>
+        <v>Header: Bearer token; Query: tab?, search?</v>
       </c>
       <c r="F163" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="164">
@@ -3673,19 +3673,19 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C164" t="str">
-        <v>/api/seller/reservations/:id</v>
+        <v>/api/seller/phone-code/confirm</v>
       </c>
       <c r="D164" t="str">
-        <v>Chi tiết đơn giữ hàng</v>
+        <v>Xác nhận OTP SĐT seller</v>
       </c>
       <c r="E164" t="str">
-        <v>Header: Bearer token; Path: :id</v>
+        <v>Header: Bearer token; Body: { phone, code }</v>
       </c>
       <c r="F164" t="str">
-        <v>{ "success": true, "data": { "reservation" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="165">
@@ -3696,16 +3696,16 @@
         <v>POST</v>
       </c>
       <c r="C165" t="str">
-        <v>/api/seller/reservations/:id/cancel</v>
+        <v>/api/seller/phone-code/request</v>
       </c>
       <c r="D165" t="str">
-        <v>Hủy đơn giữ hàng</v>
+        <v>Gửi OTP xác minh SĐT seller</v>
       </c>
       <c r="E165" t="str">
-        <v>Header: Bearer token; Path: :id; Body: { reason?, images? }</v>
+        <v>Header: Bearer token; Body: { phone }</v>
       </c>
       <c r="F165" t="str">
-        <v>{ "success": true, "data": { "reservation" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="166">
@@ -3713,16 +3713,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C166" t="str">
-        <v>/api/seller/reservations/:id/confirm</v>
+        <v>/api/seller/reservations/:id</v>
       </c>
       <c r="D166" t="str">
-        <v>Seller xác nhận giữ hàng</v>
+        <v>Chi tiết đơn giữ hàng</v>
       </c>
       <c r="E166" t="str">
-        <v>Header: Bearer token (Seller); Path: :id</v>
+        <v>Header: Bearer token; Path: :id</v>
       </c>
       <c r="F166" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -3736,16 +3736,16 @@
         <v>POST</v>
       </c>
       <c r="C167" t="str">
-        <v>/api/seller/reservations/:id/refund-dispute</v>
+        <v>/api/seller/reservations/:id/cancel</v>
       </c>
       <c r="D167" t="str">
-        <v>Seller hoàn cọc tranh chấp</v>
+        <v>Hủy đơn giữ hàng</v>
       </c>
       <c r="E167" t="str">
-        <v>Header: Bearer token (Seller); Path: :id</v>
+        <v>Header: Bearer token; Path: :id; Body: { reason?, images? }</v>
       </c>
       <c r="F167" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "reservation" } }</v>
       </c>
     </row>
     <row r="168">
@@ -3756,13 +3756,13 @@
         <v>POST</v>
       </c>
       <c r="C168" t="str">
-        <v>/api/seller/reservations/:id/reject</v>
+        <v>/api/seller/reservations/:id/confirm</v>
       </c>
       <c r="D168" t="str">
-        <v>Seller từ chối giữ hàng</v>
+        <v>Seller xác nhận giữ hàng</v>
       </c>
       <c r="E168" t="str">
-        <v>Header: Bearer token (Seller); Path: :id; Body: { reason? }</v>
+        <v>Header: Bearer token (Seller); Path: :id</v>
       </c>
       <c r="F168" t="str">
         <v>{ "success": true, "data": { "reservation" } }</v>
@@ -3776,16 +3776,16 @@
         <v>POST</v>
       </c>
       <c r="C169" t="str">
-        <v>/api/seller/reservations/:id/report-buyer</v>
+        <v>/api/seller/reservations/:id/refund-dispute</v>
       </c>
       <c r="D169" t="str">
-        <v>API /reservations/:id/report-buyer</v>
+        <v>Seller hoàn cọc tranh chấp</v>
       </c>
       <c r="E169" t="str">
-        <v>Header: Bearer token (User) + Quyền Seller; Path: :id; Body: JSON theo controller</v>
+        <v>Header: Bearer token (Seller); Path: :id</v>
       </c>
       <c r="F169" t="str">
-        <v>{ "success": true, "message": "Success", "data": {...} }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="170">
@@ -3793,19 +3793,19 @@
         <v>169</v>
       </c>
       <c r="B170" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C170" t="str">
-        <v>/api/seller/shop</v>
+        <v>/api/seller/reservations/:id/reject</v>
       </c>
       <c r="D170" t="str">
-        <v>Cài đặt shop seller</v>
+        <v>Seller từ chối giữ hàng</v>
       </c>
       <c r="E170" t="str">
-        <v>Header: Bearer token (Seller)</v>
+        <v>Header: Bearer token (Seller); Path: :id; Body: { reason? }</v>
       </c>
       <c r="F170" t="str">
-        <v>{ "success": true, "data": { "shop" } }</v>
+        <v>{ "success": true, "data": { "reservation" } }</v>
       </c>
     </row>
     <row r="171">
@@ -3813,19 +3813,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="str">
-        <v>PUT</v>
+        <v>POST</v>
       </c>
       <c r="C171" t="str">
-        <v>/api/seller/shop</v>
+        <v>/api/seller/reservations/:id/report-buyer</v>
       </c>
       <c r="D171" t="str">
-        <v>Cập nhật shop seller</v>
+        <v>API /reservations/:id/report-buyer</v>
       </c>
       <c r="E171" t="str">
-        <v>Header: Bearer token (Seller); Body: shop fields</v>
+        <v>Header: Bearer token (User) + Quyền Seller; Path: :id; Body: JSON theo controller</v>
       </c>
       <c r="F171" t="str">
-        <v>{ "success": true, "data": { "shop" } }</v>
+        <v>{ "success": true, "message": "Success", "data": {...} }</v>
       </c>
     </row>
     <row r="172">
@@ -3833,19 +3833,19 @@
         <v>171</v>
       </c>
       <c r="B172" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C172" t="str">
-        <v>/api/seller/shop/avatar</v>
+        <v>/api/seller/shop</v>
       </c>
       <c r="D172" t="str">
-        <v>Upload avatar shop</v>
+        <v>Cài đặt shop seller</v>
       </c>
       <c r="E172" t="str">
-        <v>Header: Bearer token (Seller); multipart avatar</v>
+        <v>Header: Bearer token (Seller)</v>
       </c>
       <c r="F172" t="str">
-        <v>{ "success": true, "data": { "avatar" } }</v>
+        <v>{ "success": true, "data": { "shop" } }</v>
       </c>
     </row>
     <row r="173">
@@ -3853,19 +3853,19 @@
         <v>172</v>
       </c>
       <c r="B173" t="str">
-        <v>POST</v>
+        <v>PUT</v>
       </c>
       <c r="C173" t="str">
-        <v>/api/seller/shop/username-availability</v>
+        <v>/api/seller/shop</v>
       </c>
       <c r="D173" t="str">
-        <v>Kiểm tra username shop</v>
+        <v>Cập nhật shop seller</v>
       </c>
       <c r="E173" t="str">
-        <v>Header: Bearer token; Body: { userName }</v>
+        <v>Header: Bearer token (Seller); Body: shop fields</v>
       </c>
       <c r="F173" t="str">
-        <v>{ "success": true, "data": { "available" } }</v>
+        <v>{ "success": true, "data": { "shop" } }</v>
       </c>
     </row>
     <row r="174">
@@ -3873,19 +3873,19 @@
         <v>173</v>
       </c>
       <c r="B174" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C174" t="str">
-        <v>/api/seller/stats</v>
+        <v>/api/seller/shop/avatar</v>
       </c>
       <c r="D174" t="str">
-        <v>Thống kê seller</v>
+        <v>Upload avatar shop</v>
       </c>
       <c r="E174" t="str">
-        <v>Header: Bearer token (Seller)</v>
+        <v>Header: Bearer token (Seller); multipart avatar</v>
       </c>
       <c r="F174" t="str">
-        <v>{ "success": true, "data": { "stats" } }</v>
+        <v>{ "success": true, "data": { "avatar" } }</v>
       </c>
     </row>
     <row r="175">
@@ -3893,19 +3893,19 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C175" t="str">
-        <v>/api/seller/subscription</v>
+        <v>/api/seller/shop/username-availability</v>
       </c>
       <c r="D175" t="str">
-        <v>Gói đăng ký seller hiện tại</v>
+        <v>Kiểm tra username shop</v>
       </c>
       <c r="E175" t="str">
-        <v>Header: Bearer token (Seller)</v>
+        <v>Header: Bearer token; Body: { userName }</v>
       </c>
       <c r="F175" t="str">
-        <v>{ "success": true, "data": { "subscription" } }</v>
+        <v>{ "success": true, "data": { "available" } }</v>
       </c>
     </row>
     <row r="176">
@@ -3913,19 +3913,19 @@
         <v>175</v>
       </c>
       <c r="B176" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C176" t="str">
-        <v>/api/seller/subscription/purchase</v>
+        <v>/api/seller/stats</v>
       </c>
       <c r="D176" t="str">
-        <v>Mua gói seller</v>
+        <v>Thống kê seller</v>
       </c>
       <c r="E176" t="str">
-        <v>Header: Bearer token (Seller); Body: { planId }</v>
+        <v>Header: Bearer token (Seller)</v>
       </c>
       <c r="F176" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "stats" } }</v>
       </c>
     </row>
     <row r="177">
@@ -3933,19 +3933,19 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C177" t="str">
-        <v>/api/seller/verification</v>
+        <v>/api/seller/subscription</v>
       </c>
       <c r="D177" t="str">
-        <v>Nộp hồ sơ xác minh seller</v>
+        <v>Gói đăng ký seller hiện tại</v>
       </c>
       <c r="E177" t="str">
-        <v>Header: Bearer token; Body: { shopName, documents, ... }</v>
+        <v>Header: Bearer token (Seller)</v>
       </c>
       <c r="F177" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "subscription" } }</v>
       </c>
     </row>
     <row r="178">
@@ -3956,13 +3956,13 @@
         <v>POST</v>
       </c>
       <c r="C178" t="str">
-        <v>/api/seller/verification/:id/approve</v>
+        <v>/api/seller/subscription/purchase</v>
       </c>
       <c r="D178" t="str">
-        <v>Admin duyệt seller</v>
+        <v>Mua gói seller</v>
       </c>
       <c r="E178" t="str">
-        <v>Header: Bearer token (Admin); Path: :id</v>
+        <v>Header: Bearer token (Seller); Body: { planId }</v>
       </c>
       <c r="F178" t="str">
         <v>{ "success": true }</v>
@@ -3976,13 +3976,13 @@
         <v>POST</v>
       </c>
       <c r="C179" t="str">
-        <v>/api/seller/verification/:id/reject</v>
+        <v>/api/seller/verification</v>
       </c>
       <c r="D179" t="str">
-        <v>Admin từ chối seller</v>
+        <v>Nộp hồ sơ xác minh seller</v>
       </c>
       <c r="E179" t="str">
-        <v>Header: Bearer token (Admin); Path: :id; Body: { note? }</v>
+        <v>Header: Bearer token; Body: { shopName, documents, ... }</v>
       </c>
       <c r="F179" t="str">
         <v>{ "success": true }</v>
@@ -3993,19 +3993,19 @@
         <v>179</v>
       </c>
       <c r="B180" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C180" t="str">
-        <v>/api/seller/verification/admin</v>
+        <v>/api/seller/verification/:id/approve</v>
       </c>
       <c r="D180" t="str">
-        <v>Admin: tất cả hồ sơ seller</v>
+        <v>Admin duyệt seller</v>
       </c>
       <c r="E180" t="str">
-        <v>Header: Bearer token (Admin); Query: status?</v>
+        <v>Header: Bearer token (Admin); Path: :id</v>
       </c>
       <c r="F180" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="181">
@@ -4013,19 +4013,19 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C181" t="str">
-        <v>/api/seller/verification/me</v>
+        <v>/api/seller/verification/:id/reject</v>
       </c>
       <c r="D181" t="str">
-        <v>Trạng thái xác minh seller</v>
+        <v>Admin từ chối seller</v>
       </c>
       <c r="E181" t="str">
-        <v>Header: Bearer token (User)</v>
+        <v>Header: Bearer token (Admin); Path: :id; Body: { note? }</v>
       </c>
       <c r="F181" t="str">
-        <v>{ "success": true, "data": { "verification" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="182">
@@ -4036,13 +4036,13 @@
         <v>GET</v>
       </c>
       <c r="C182" t="str">
-        <v>/api/seller/verification/pending</v>
+        <v>/api/seller/verification/admin</v>
       </c>
       <c r="D182" t="str">
-        <v>Admin: hồ sơ seller chờ duyệt</v>
+        <v>Admin: tất cả hồ sơ seller</v>
       </c>
       <c r="E182" t="str">
-        <v>Header: Bearer token (Admin)</v>
+        <v>Header: Bearer token (Admin); Query: status?</v>
       </c>
       <c r="F182" t="str">
         <v>{ "success": true, "data": { "items" } }</v>
@@ -4056,16 +4056,16 @@
         <v>GET</v>
       </c>
       <c r="C183" t="str">
-        <v>/api/shops/:id</v>
+        <v>/api/seller/verification/me</v>
       </c>
       <c r="D183" t="str">
-        <v>Chi tiết shop public</v>
+        <v>Trạng thái xác minh seller</v>
       </c>
       <c r="E183" t="str">
-        <v>Path: :id</v>
+        <v>Header: Bearer token (User)</v>
       </c>
       <c r="F183" t="str">
-        <v>{ "success": true, "data": { "shop" } }</v>
+        <v>{ "success": true, "data": { "verification" } }</v>
       </c>
     </row>
     <row r="184">
@@ -4076,13 +4076,13 @@
         <v>GET</v>
       </c>
       <c r="C184" t="str">
-        <v>/api/shops/:id/products</v>
+        <v>/api/seller/verification/pending</v>
       </c>
       <c r="D184" t="str">
-        <v>Sản phẩm của shop</v>
+        <v>Admin: hồ sơ seller chờ duyệt</v>
       </c>
       <c r="E184" t="str">
-        <v>Path: :id; Query: page?, limit?</v>
+        <v>Header: Bearer token (Admin)</v>
       </c>
       <c r="F184" t="str">
         <v>{ "success": true, "data": { "items" } }</v>
@@ -4096,16 +4096,16 @@
         <v>GET</v>
       </c>
       <c r="C185" t="str">
-        <v>/api/shops/:id/promotions</v>
+        <v>/api/shops/:id</v>
       </c>
       <c r="D185" t="str">
-        <v>API /shops/:id/promotions</v>
+        <v>Chi tiết shop public</v>
       </c>
       <c r="E185" t="str">
-        <v>Path: :id; Query: page?, limit?, q?, ...</v>
+        <v>Path: :id</v>
       </c>
       <c r="F185" t="str">
-        <v>{ "success": true, "message": "Success", "data": {...} }</v>
+        <v>{ "success": true, "data": { "shop" } }</v>
       </c>
     </row>
     <row r="186">
@@ -4116,13 +4116,13 @@
         <v>GET</v>
       </c>
       <c r="C186" t="str">
-        <v>/api/shops/:id/reviews</v>
+        <v>/api/shops/:id/products</v>
       </c>
       <c r="D186" t="str">
-        <v>Đánh giá shop</v>
+        <v>Sản phẩm của shop</v>
       </c>
       <c r="E186" t="str">
-        <v>Path: :id; Query: page?</v>
+        <v>Path: :id; Query: page?, limit?</v>
       </c>
       <c r="F186" t="str">
         <v>{ "success": true, "data": { "items" } }</v>
@@ -4136,16 +4136,16 @@
         <v>GET</v>
       </c>
       <c r="C187" t="str">
-        <v>/api/shops/categories</v>
+        <v>/api/shops/:id/promotions</v>
       </c>
       <c r="D187" t="str">
-        <v>DM shop admin</v>
+        <v>API /shops/:id/promotions</v>
       </c>
       <c r="E187" t="str">
-        <v>Header: Bearer token (Admin)</v>
+        <v>Path: :id; Query: page?, limit?, q?, ...</v>
       </c>
       <c r="F187" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true, "message": "Success", "data": {...} }</v>
       </c>
     </row>
     <row r="188">
@@ -4156,16 +4156,16 @@
         <v>GET</v>
       </c>
       <c r="C188" t="str">
-        <v>/api/shops/nearby</v>
+        <v>/api/shops/:id/reviews</v>
       </c>
       <c r="D188" t="str">
-        <v>Danh sách shop gần vị trí</v>
+        <v>Đánh giá shop</v>
       </c>
       <c r="E188" t="str">
-        <v>Query: lat, lng, radius?, limit?</v>
+        <v>Path: :id; Query: page?</v>
       </c>
       <c r="F188" t="str">
-        <v>{ "success": true, "data": { "items": [...] } }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="189">
@@ -4176,16 +4176,16 @@
         <v>GET</v>
       </c>
       <c r="C189" t="str">
-        <v>/api/shops/search</v>
+        <v>/api/shops/categories</v>
       </c>
       <c r="D189" t="str">
-        <v>Tìm kiếm shop</v>
+        <v>DM shop admin</v>
       </c>
       <c r="E189" t="str">
-        <v>Query: q, page?, limit?</v>
+        <v>Header: Bearer token (Admin)</v>
       </c>
       <c r="F189" t="str">
-        <v>{ "success": true, "data": { "items", "total" } }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="190">
@@ -4196,16 +4196,16 @@
         <v>GET</v>
       </c>
       <c r="C190" t="str">
-        <v>/api/wallet/</v>
+        <v>/api/shops/nearby</v>
       </c>
       <c r="D190" t="str">
-        <v>Số dư ví</v>
+        <v>Danh sách shop gần vị trí</v>
       </c>
       <c r="E190" t="str">
-        <v>Header: Bearer token (User)</v>
+        <v>Query: lat, lng, radius?, limit?</v>
       </c>
       <c r="F190" t="str">
-        <v>{ "success": true, "data": { "balance" } }</v>
+        <v>{ "success": true, "data": { "items": [...] } }</v>
       </c>
     </row>
     <row r="191">
@@ -4216,16 +4216,16 @@
         <v>GET</v>
       </c>
       <c r="C191" t="str">
-        <v>/api/wallet/banks</v>
+        <v>/api/shops/search</v>
       </c>
       <c r="D191" t="str">
-        <v>Ngân hàng hỗ trợ rút tiền</v>
+        <v>Tìm kiếm shop</v>
       </c>
       <c r="E191" t="str">
-        <v>Header: Bearer token</v>
+        <v>Query: q, page?, limit?</v>
       </c>
       <c r="F191" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true, "data": { "items", "total" } }</v>
       </c>
     </row>
     <row r="192">
@@ -4233,19 +4233,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C192" t="str">
-        <v>/api/wallet/topup</v>
+        <v>/api/wallet/</v>
       </c>
       <c r="D192" t="str">
-        <v>Tạo link nạp tiền PayOS</v>
+        <v>Số dư ví</v>
       </c>
       <c r="E192" t="str">
-        <v>Header: Bearer token; Body: { amount }</v>
+        <v>Header: Bearer token (User)</v>
       </c>
       <c r="F192" t="str">
-        <v>{ "success": true, "data": { "checkoutUrl", "orderCode" } }</v>
+        <v>{ "success": true, "data": { "balance" } }</v>
       </c>
     </row>
     <row r="193">
@@ -4253,19 +4253,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C193" t="str">
-        <v>/api/wallet/topup/cancel</v>
+        <v>/api/wallet/banks</v>
       </c>
       <c r="D193" t="str">
-        <v>Hủy phiên nạp tiền</v>
+        <v>Ngân hàng hỗ trợ rút tiền</v>
       </c>
       <c r="E193" t="str">
-        <v>Header: Bearer token; Body: { orderCode }</v>
+        <v>Header: Bearer token</v>
       </c>
       <c r="F193" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": [...] }</v>
       </c>
     </row>
     <row r="194">
@@ -4276,16 +4276,16 @@
         <v>POST</v>
       </c>
       <c r="C194" t="str">
-        <v>/api/wallet/topup/sync</v>
+        <v>/api/wallet/topup</v>
       </c>
       <c r="D194" t="str">
-        <v>Đồng bộ trạng thái nạp tiền</v>
+        <v>Tạo link nạp tiền PayOS</v>
       </c>
       <c r="E194" t="str">
-        <v>Header: Bearer token; Body: { orderCode }</v>
+        <v>Header: Bearer token; Body: { amount }</v>
       </c>
       <c r="F194" t="str">
-        <v>{ "success": true, "data": { "wallet", "transaction" } }</v>
+        <v>{ "success": true, "data": { "checkoutUrl", "orderCode" } }</v>
       </c>
     </row>
     <row r="195">
@@ -4293,19 +4293,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C195" t="str">
-        <v>/api/wallet/transactions</v>
+        <v>/api/wallet/topup/cancel</v>
       </c>
       <c r="D195" t="str">
-        <v>Lịch sử giao dịch ví</v>
+        <v>Hủy phiên nạp tiền</v>
       </c>
       <c r="E195" t="str">
-        <v>Header: Bearer token; Query: page?, limit?</v>
+        <v>Header: Bearer token; Body: { orderCode }</v>
       </c>
       <c r="F195" t="str">
-        <v>{ "success": true, "data": { "items" } }</v>
+        <v>{ "success": true }</v>
       </c>
     </row>
     <row r="196">
@@ -4313,19 +4313,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>GET</v>
+        <v>POST</v>
       </c>
       <c r="C196" t="str">
-        <v>/api/wallet/transactions/:id</v>
+        <v>/api/wallet/topup/sync</v>
       </c>
       <c r="D196" t="str">
-        <v>Chi tiết giao dịch ví</v>
+        <v>Đồng bộ trạng thái nạp tiền</v>
       </c>
       <c r="E196" t="str">
-        <v>Header: Bearer token; Path: :id</v>
+        <v>Header: Bearer token; Body: { orderCode }</v>
       </c>
       <c r="F196" t="str">
-        <v>{ "success": true, "data": { "transaction" } }</v>
+        <v>{ "success": true, "data": { "wallet", "transaction" } }</v>
       </c>
     </row>
     <row r="197">
@@ -4333,19 +4333,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>POST</v>
+        <v>GET</v>
       </c>
       <c r="C197" t="str">
-        <v>/api/wallet/withdraw</v>
+        <v>/api/wallet/transactions</v>
       </c>
       <c r="D197" t="str">
-        <v>Tạo yêu cầu rút tiền</v>
+        <v>Lịch sử giao dịch ví</v>
       </c>
       <c r="E197" t="str">
-        <v>Header: Bearer token; Body: { amount, bankId, accountNumber, accountName }</v>
+        <v>Header: Bearer token; Query: page?, limit?</v>
       </c>
       <c r="F197" t="str">
-        <v>{ "success": true, "data": { "withdraw", "wallet" } }</v>
+        <v>{ "success": true, "data": { "items" } }</v>
       </c>
     </row>
     <row r="198">
@@ -4356,16 +4356,16 @@
         <v>GET</v>
       </c>
       <c r="C198" t="str">
-        <v>/api/wallet/withdraws</v>
+        <v>/api/wallet/transactions/:id</v>
       </c>
       <c r="D198" t="str">
-        <v>Lịch sử rút tiền</v>
+        <v>Chi tiết giao dịch ví</v>
       </c>
       <c r="E198" t="str">
-        <v>Header: Bearer token</v>
+        <v>Header: Bearer token; Path: :id</v>
       </c>
       <c r="F198" t="str">
-        <v>{ "success": true, "data": [...] }</v>
+        <v>{ "success": true, "data": { "transaction" } }</v>
       </c>
     </row>
     <row r="199">
@@ -4376,16 +4376,16 @@
         <v>POST</v>
       </c>
       <c r="C199" t="str">
-        <v>/api/webhooks/payos</v>
+        <v>/api/wallet/withdraw</v>
       </c>
       <c r="D199" t="str">
-        <v>Webhook PayOS xác nhận nạp tiền</v>
+        <v>Tạo yêu cầu rút tiền</v>
       </c>
       <c r="E199" t="str">
-        <v>Body: PayOS callback payload</v>
+        <v>Header: Bearer token; Body: { amount, bankId, accountNumber, accountName }</v>
       </c>
       <c r="F199" t="str">
-        <v>{ "success": true }</v>
+        <v>{ "success": true, "data": { "withdraw", "wallet" } }</v>
       </c>
     </row>
     <row r="200">
@@ -4396,21 +4396,61 @@
         <v>GET</v>
       </c>
       <c r="C200" t="str">
+        <v>/api/wallet/withdraws</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Lịch sử rút tiền</v>
+      </c>
+      <c r="E200" t="str">
+        <v>Header: Bearer token</v>
+      </c>
+      <c r="F200" t="str">
+        <v>{ "success": true, "data": [...] }</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C201" t="str">
+        <v>/api/webhooks/payos</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Webhook PayOS xác nhận nạp tiền</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Body: PayOS callback payload</v>
+      </c>
+      <c r="F201" t="str">
+        <v>{ "success": true }</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C202" t="str">
         <v>/health</v>
       </c>
-      <c r="D200" t="str">
+      <c r="D202" t="str">
         <v>Health check</v>
       </c>
-      <c r="E200" t="str">
+      <c r="E202" t="str">
         <v>—</v>
       </c>
-      <c r="F200" t="str">
+      <c r="F202" t="str">
         <v>{ "success": true, "message": "OK" }</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F202"/>
   </ignoredErrors>
 </worksheet>
 </file>
